--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44743-2025 artfynd.xlsx
+++ b/artfynd/A 44743-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738077</v>
       </c>
       <c r="B2" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
